--- a/journal_analyzer/graphy/task_list_graphy.xlsx
+++ b/journal_analyzer/graphy/task_list_graphy.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="17" activeTab="18" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="13" activeTab="13" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,8 +21,8 @@
     <sheet name="특수관계자 분석" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="리스완전성" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="거래처분석" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
@@ -37,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -70,38 +71,31 @@
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
+      <family val="3"/>
+      <i val="1"/>
+      <color rgb="FF7F6000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
       <family val="3"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F6000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <i val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="FF375623"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -129,26 +123,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
+        <fgColor rgb="FF70AD47"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -182,17 +176,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -201,7 +207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -227,46 +233,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -636,12 +643,12 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="21" min="1" max="1"/>
+    <col width="22" customWidth="1" style="21" min="2" max="2"/>
+    <col width="30" customWidth="1" style="21" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="21">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
@@ -658,7 +665,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="16" customHeight="1" s="21">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ClientName</t>
@@ -671,7 +678,7 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="16" customHeight="1" s="21">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>StartDate</t>
@@ -688,7 +695,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="16" customHeight="1" s="21">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EndDate</t>
@@ -701,7 +708,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="16" customHeight="1" s="21">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TargetYear</t>
@@ -726,7 +733,7 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30.58203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="30.58203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,8 +762,8 @@
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="34.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="34.08203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,10 +794,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="40.9140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="40.9140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,6 +809,30 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>주식회사 디지털그래피</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRAPHY SMA, INC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -816,11 +847,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="10.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="14.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,6 +863,114 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>지급임차료(제)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>차량유지비(제)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>지급수수료(제)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>건물관리비(제)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>건물관리비</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>경상연구개발비</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -846,13 +985,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="10.83203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>기타제예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>정기예.적금</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>별단예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>미수수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>미지급비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>유동성장기부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>리스부채(유동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>리스부채(비유동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>이자비용(리스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>지급수수료(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
         </is>
       </c>
     </row>
@@ -864,183 +1125,202 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00ED7D31"/>
+    <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" style="21" min="1" max="1"/>
+    <col width="34.9140625" customWidth="1" style="21" min="2" max="2"/>
+    <col width="35" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="21" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="21">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" s="21">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>작업명</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>거래처명</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="21">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>분析01</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr"/>
-      <c r="C3" s="18" t="inlineStr"/>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Frontier Inc</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="21">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>분析02</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr"/>
-      <c r="C4" s="18" t="inlineStr"/>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Corefront</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="21">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>분析03</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr"/>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>AB Med Inc.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="21">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>분析04</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr"/>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>분析05</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>BILAL BE</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="18" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="18" t="inlineStr"/>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="18" t="inlineStr"/>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr"/>
-      <c r="B12" s="18" t="inlineStr"/>
-      <c r="C12" s="18" t="inlineStr"/>
-      <c r="D12" s="19" t="inlineStr"/>
-      <c r="E12" s="19" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="21">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="21">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="21">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="21">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="21">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="21">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1053,152 +1333,1677 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="FF70AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" style="21" min="1" max="1"/>
+    <col width="10" customWidth="1" style="21" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="21">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" s="21">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>손익구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="21">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+    </row>
+    <row r="4" ht="18" customHeight="1" s="21">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="21">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="21">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="21">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>임대료수입</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="21">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>기타매출</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="21">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>원자재매출</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="21">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>A/S매출</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>운송료매출</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>서비스매출</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>급여(제)</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>판매비와관리비</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>영업외수익</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>영업외비용</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr"/>
-      <c r="C8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr"/>
-      <c r="C9" s="19" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="19" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="19" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr"/>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="19" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>퇴직급여(제)</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>상여금(제)</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>복리후생비(제)</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>여비교통비_국내(제)</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>여비교통비_해외(제)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>접대비(제)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>통신비(제)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>수도광열비(제)</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>전력비(제)</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>세금과공과금(제)</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>감가상각비(제)</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>지급임차료(제)</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>수선비(제)</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>보험료(제)</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>차량유지비(제)</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>운반비(제)</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>교육훈련비(제)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>도서인쇄비(제)</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>사무용품비(제)</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>소모품비(제)</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>지급수수료(제)</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>외주가공비(제)</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>감가상각비(리스)</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>건물관리비(제)</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>외주가공비(DG)</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>직원급여</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>상여금</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>잡급</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>퇴직급여</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>여비교통비</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>여비교통비_국내</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>여비교통비_해외</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>접대비_경조사</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>접대비_기타</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>통신비</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>수도광열비</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>세금과공과금</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>감가상각비(리스)</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>감가상각비(국)</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>수선비</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>운반비</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>교육훈련비</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>도서인쇄비</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>사무용품비</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>소모품비</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>회계감사수수료</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>법무자문수수료</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>협회비</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>건물관리비</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>무형고정자산상각비</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>견본비</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>대손상각비</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>주식보상비용</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>경상연구개발비</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>세금과공과금(과태료)</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -1213,11 +3018,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" style="21" min="1" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1229,6 +3033,42 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1243,14 +3083,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" style="21" min="1" max="1"/>
+    <col width="10" customWidth="1" style="21" min="2" max="2"/>
+    <col width="12" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="21" min="4" max="4"/>
+    <col width="55" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1277,6 +3117,125 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비(제)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>감가상각비(리스)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>감가상각비(리스)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>감가상각비(국)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>유형자산처분손실</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1291,13 +3250,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" style="21" min="1" max="1"/>
+    <col width="26" customWidth="1" style="21" min="2" max="2"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
+    <col width="21.83203125" customWidth="1" style="21" min="4" max="4"/>
+    <col width="21.9140625" customWidth="1" style="21" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="21" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1334,6 +3295,154 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>감가상각누계액(건물)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>감가상각누계액(기계장치)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>감가상각누계액(차량운반구)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>공구와기구</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>감가상각누계액(공구와기구)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>공구와기구</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>공구와기구(국)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>감가상각누계액(비품)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>감가상각누계액(시설장치)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>감가상각누계액(리스)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1348,16 +3457,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="72.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="21" min="1" max="1"/>
+    <col width="28.83203125" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
+    <col width="85.9140625" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
+    <col width="12" customWidth="1" style="21" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="21">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>분석번호</t>
@@ -1378,19 +3487,19 @@
           <t>실행여부</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>분석대상</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>기준월</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="16" customHeight="1" s="21">
+      <c r="A2" s="9" t="n">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1405,7 +3514,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1417,8 +3526,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="12" t="n">
+    <row r="3" ht="16" customHeight="1" s="21">
+      <c r="A3" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1433,91 +3542,91 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="21">
+      <c r="A4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>데이터 개요</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="21">
+      <c r="A5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>계정명 리스트</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="21">
+      <c r="A6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>사원별 집계</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>당기</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>데이터 개요</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>계정명 리스트</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>사원별 집계</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="16" customHeight="1" s="21">
       <c r="A7" s="6" t="n">
         <v>7</v>
       </c>
@@ -1558,7 +3667,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1608,7 +3717,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1633,7 +3742,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1683,7 +3792,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1708,7 +3817,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1783,7 +3892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1908,7 +4017,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1958,7 +4067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1968,12 +4077,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="7" t="n">
         <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손익월별분析</t>
+          <t>손익월별분석</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1983,7 +4092,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1992,58 +4101,57 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
+    <row r="26">
+      <c r="A26" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>AI계정별분석_실행</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립적으로 실행)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>AI계정별분석_실행</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립적으로 실행)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="A27" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>감가상각_평가손익분석</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>당기</t>
         </is>
       </c>
-      <c r="F27" s="22" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="22" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>감가상각_평가손익분석</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="n"/>
+      <c r="F27" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2057,7 +4165,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.33203125" bestFit="1" customWidth="1" style="21" min="1" max="2"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
+    <col width="4.83203125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2092,16 +4205,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>원자재매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A/S매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>운송료매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>서비스매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>미지급금(카드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>미지급금(외화)</t>
         </is>
       </c>
     </row>
@@ -2119,7 +4309,7 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="28.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.9140625" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2145,15 +4335,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.33203125" customWidth="1" min="2" max="2"/>
-    <col width="15.75" customWidth="1" min="3" max="3"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="14.33203125" customWidth="1" style="21" min="2" max="2"/>
+    <col width="15.75" customWidth="1" style="21" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="21">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -2172,6 +4362,108 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>운송료매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>서비스매출</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2186,12 +4478,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="9.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="17" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="12.83203125" customWidth="1" style="21" min="2" max="2"/>
+    <col width="12.08203125" customWidth="1" style="21" min="3" max="3"/>
+    <col width="17" bestFit="1" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2218,6 +4511,159 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>선급금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2232,16 +4678,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="10" customWidth="1" style="21" min="2" max="2"/>
+    <col width="12" customWidth="1" style="21" min="3" max="3"/>
+    <col width="42" customWidth="1" style="21" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="21">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -2263,7 +4709,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="16" customHeight="1" s="21">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>외상매출금</t>
@@ -2281,7 +4727,7 @@
       </c>
       <c r="D2" s="8" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="16" customHeight="1" s="21">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>선급금</t>
@@ -2299,10 +4745,10 @@
       </c>
       <c r="D3" s="8" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="16" customHeight="1" s="21">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>외주가공비(제조)</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -2317,7 +4763,7 @@
       </c>
       <c r="D4" s="8" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="16" customHeight="1" s="21">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>외상매입금</t>
@@ -2335,15 +4781,15 @@
       </c>
       <c r="D5" s="8" t="n"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>제예금(보통예금)</t>
+    <row r="6" ht="16" customHeight="1" s="21">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>미지급금</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -2351,12 +4797,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
+      <c r="D6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" s="21">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>제예금(보통예금)</t>
+          <t>국내상품매출액</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2371,10 +4817,10 @@
       </c>
       <c r="D7" s="8" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="16" customHeight="1" s="21">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>상품매출_국내</t>
+          <t>해외상품매출액</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -2389,10 +4835,10 @@
       </c>
       <c r="D8" s="8" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="16" customHeight="1" s="21">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>제품매출(외주)_국내</t>
+          <t>국내제품매출액</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2407,10 +4853,10 @@
       </c>
       <c r="D9" s="8" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="16" customHeight="1" s="21">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>제품매출(자사)_국내</t>
+          <t>해외제품매출액</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -2424,28 +4870,6 @@
         </is>
       </c>
       <c r="D10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>전체 계정 — 데이터 많을 경우 느릴 수 있음</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2458,17 +4882,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" style="21" min="1" max="1"/>
+    <col width="10" customWidth="1" style="21" min="2" max="2"/>
+    <col width="14" customWidth="1" style="21" min="3" max="3"/>
+    <col width="12" customWidth="1" style="21" min="4" max="4"/>
+    <col width="36" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="21">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -2495,9 +4919,186 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1"/>
-    <row r="3" ht="16" customHeight="1"/>
-    <row r="4" ht="16" customHeight="1"/>
+    <row r="2" ht="16" customHeight="1" s="21">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="21">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>선급금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="21">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2509,10 +5110,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2527,6 +5128,750 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>운송료매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>수익</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>서비스매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>여비교통비_국내(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>여비교통비_해외(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>접대비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>통신비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>수도광열비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>전력비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>세금과공과금(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>감가상각비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>지급임차료(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>수선비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>보험료(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>차량유지비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>운반비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>교육훈련비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>도서인쇄비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>사무용품비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>소모품비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>지급수수료(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>외주가공비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>감가상각비(리스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>건물관리비(제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>외주가공비(DG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>여비교통비</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>여비교통비_국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>여비교통비_해외</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>접대비_경조사</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>접대비_기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>통신비</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>수도광열비</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>세금과공과금</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>감가상각비(리스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>감가상각비(국)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>수선비</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>운반비</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>교육훈련비</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>도서인쇄비</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>사무용품비</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>소모품비</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>회계감사수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>법무자문수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>협회비</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>건물관리비</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>무형고정자산상각비</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>견본비</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>대손상각비</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>주식보상비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>경상연구개발비</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>세금과공과금(과태료)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/journal_analyzer/graphy/task_list_graphy.xlsx
+++ b/journal_analyzer/graphy/task_list_graphy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="17" activeTab="18" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="14" activeTab="15" autoFilterDateGrouping="1"/>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="13" activeTab="13" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
@@ -1337,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25" customWidth="1" style="21" min="1" max="1"/>
@@ -1464,7 +1464,7 @@
     <row r="7" ht="18" customHeight="1" s="21">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>임대료수입</t>
+          <t>원자재매출</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="8" ht="18" customHeight="1" s="21">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>기타매출</t>
+          <t>A/S매출</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -1506,9 +1506,9 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="21">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>원자재매출</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>운송료매출</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -1528,9 +1528,9 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="21">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>A/S매출</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>서비스매출</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>운송료매출</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>대변</t>
+          <t>급여(제)</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>매출원가</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>서비스매출</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>대변</t>
+          <t>퇴직급여(제)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -1589,14 +1589,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>매출원가</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>급여(제)</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
@@ -1618,7 +1618,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>퇴직급여(제)</t>
+          <t>여비교통비_국내(제)</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>상여금(제)</t>
+          <t>여비교통비_해외(제)</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>복리후생비(제)</t>
+          <t>접대비(제)</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>여비교통비_국내(제)</t>
+          <t>통신비(제)</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
@@ -1706,7 +1706,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>여비교통비_해외(제)</t>
+          <t>수도광열비(제)</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
@@ -1728,7 +1728,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>접대비(제)</t>
+          <t>감가상각비(제)</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>통신비(제)</t>
+          <t>지급임차료(제)</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>수도광열비(제)</t>
+          <t>수선비(제)</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
@@ -1794,7 +1794,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>전력비(제)</t>
+          <t>보험료(제)</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>세금과공과금(제)</t>
+          <t>차량유지비(제)</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
@@ -1838,7 +1838,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>감가상각비(제)</t>
+          <t>운반비(제)</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
@@ -1860,7 +1860,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>지급임차료(제)</t>
+          <t>교육훈련비(제)</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>수선비(제)</t>
+          <t>사무용품비(제)</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -1904,7 +1904,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>보험료(제)</t>
+          <t>소모품비(제)</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>차량유지비(제)</t>
+          <t>지급수수료(제)</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -1948,7 +1948,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>운반비(제)</t>
+          <t>외주가공비</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>교육훈련비(제)</t>
+          <t>감가상각비(리스)(제)</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>도서인쇄비(제)</t>
+          <t>건물관리비(제)</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>사무용품비(제)</t>
+          <t>직원급여</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -2029,14 +2029,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>소모품비(제)</t>
+          <t>잡급</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
@@ -2051,14 +2051,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>지급수수료(제)</t>
+          <t>퇴직급여</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -2073,14 +2073,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>외주가공비(제)</t>
+          <t>복리후생비</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
@@ -2095,14 +2095,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>감가상각비(리스)</t>
+          <t>여비교통비_국내</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -2117,14 +2117,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>건물관리비(제)</t>
+          <t>여비교통비_해외</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -2139,14 +2139,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>외주가공비(DG)</t>
+          <t>접대비</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>직원급여</t>
+          <t>접대비_경조사</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -2190,7 +2190,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>상여금</t>
+          <t>통신비</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>잡급</t>
+          <t>수도광열비</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>퇴직급여</t>
+          <t>세금과공과금</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
@@ -2256,7 +2256,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
@@ -2278,7 +2278,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>여비교통비</t>
+          <t>감가상각비(리스)</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
@@ -2300,7 +2300,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>여비교통비_국내</t>
+          <t>감가상각비(국)</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>여비교통비_해외</t>
+          <t>지급임차료</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>접대비</t>
+          <t>수선비</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
@@ -2366,7 +2366,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>접대비_경조사</t>
+          <t>보험료</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
@@ -2388,7 +2388,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>접대비_기타</t>
+          <t>차량유지비</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>운반비</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -2432,7 +2432,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>수도광열비</t>
+          <t>교육훈련비</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>세금과공과금</t>
+          <t>도서인쇄비</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>사무용품비</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>감가상각비(리스)</t>
+          <t>소모품비</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
@@ -2520,7 +2520,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>감가상각비(국)</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
@@ -2542,7 +2542,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>지급임차료</t>
+          <t>회계감사수수료</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
@@ -2564,7 +2564,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>법무자문수수료</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>보험료</t>
+          <t>광고선전비</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
@@ -2608,7 +2608,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>차량유지비</t>
+          <t>건물관리비</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
@@ -2630,7 +2630,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>운반비</t>
+          <t>무형고정자산상각</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>교육훈련비</t>
+          <t>견본비</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>도서인쇄비</t>
+          <t>대손상각비</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>사무용품비</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
@@ -2718,7 +2718,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>소모품비</t>
+          <t>경상연구개발비</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>세금과공과금(과태료)</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
@@ -2759,251 +2759,6 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>회계감사수수료</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>법무자문수수료</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>광고선전비</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>협회비</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>건물관리비</t>
-        </is>
-      </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>무형고정자산상각비</t>
-        </is>
-      </c>
-      <c r="B71" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>견본비</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>대손상각비</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>경상연구개발비</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>세금과공과금(과태료)</t>
-        </is>
-      </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -3140,7 +2895,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>감가상각비(리스)</t>
+          <t>감가상각비(리스)(제)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/journal_analyzer/graphy/task_list_graphy.xlsx
+++ b/journal_analyzer/graphy/task_list_graphy.xlsx
@@ -3,30 +3,31 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="14" activeTab="15" autoFilterDateGrouping="1"/>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="13" activeTab="13" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="심층분석 (계정별 Top) " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="총계정원장" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="벤포드 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="라운드넘버 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="계정별 상세거래내역" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="특수관계자 분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="리스완전성" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="거래처분석" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="유형자산_처분손익" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="02_거래처 전기_당기 비교" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_벤포드 분석" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="08_상대계정 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="10_라운드넘버 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="11_특수관계자 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="12_자산 vs 부채 교차" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="17_거래처분석" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="21_총계정원장" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="22_은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="24_리스완전성" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="25_손익월별분석" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Sheet1" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -730,21 +731,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30.58203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>계정명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>구분</t>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>원자재매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A/S매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>운송료매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>서비스매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>미지급금(카드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>미지급금(외화)</t>
         </is>
       </c>
     </row>
@@ -756,35 +829,208 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="34.08203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
+    <col width="18" customWidth="1" style="21" min="1" max="1"/>
+    <col width="34.9140625" customWidth="1" style="21" min="2" max="2"/>
+    <col width="35" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="21" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="21">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="21">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액유형</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
+    <row r="3" ht="18" customHeight="1" s="21">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>분析01</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Frontier Inc</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="21">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>분析02</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Corefront</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="21">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>분析03</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>AB Med Inc.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="21">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>분析04</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>BILAL BE</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="21">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="21">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="21">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="21">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="21">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="21">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -797,47 +1043,47 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="40.9140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="30.58203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>거래처명</t>
+          <t>계정명</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>실행여부</t>
+          <t>구분</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>주식회사 디지털그래피</t>
+          <t>외상매출금</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>자산</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRAPHY SMA, INC</t>
+          <t>외상매입금</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>부채</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -847,130 +1093,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="14.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
+    <col width="28.9140625" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>지급임차료(제)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>차량유지비(제)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>지급수수료(제)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>건물관리비(제)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>지급임차료</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>차량유지비</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>지급수수료</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>건물관리비</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>경상연구개발비</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1125,212 +1262,177 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="21" min="1" max="1"/>
-    <col width="34.9140625" customWidth="1" style="21" min="2" max="2"/>
-    <col width="35" customWidth="1" style="21" min="3" max="3"/>
-    <col width="10" customWidth="1" style="21" min="4" max="5"/>
+    <col width="34.08203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="21">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>작업명</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액유형</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="21">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>분析01</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Frontier Inc</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" s="21">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>분析02</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Corefront</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="21">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>분析03</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>AB Med Inc.</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="21">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>분析04</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>해외제품매출액, 해외상품매출액,외상매출금</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>BILAL BE</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" s="21">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="21">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="21">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="21">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="21">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="21">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>지급임차료(제)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>차량유지비(제)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>지급수수료(제)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>건물관리비(제)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>건물관리비</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>경상연구개발비</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -2767,7 +2869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2832,7 +2934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2989,213 +3091,6 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="22" customWidth="1" style="21" min="1" max="1"/>
-    <col width="26" customWidth="1" style="21" min="2" max="2"/>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
-    <col width="21.83203125" customWidth="1" style="21" min="4" max="4"/>
-    <col width="21.9140625" customWidth="1" style="21" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="21" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>유형자산계정명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>감가상각누계액계정명</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>대체상대계정</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>취득원가_수동조정</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>상각누계액_수동조정</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>토지</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>건물</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>감가상각누계액(건물)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>기계장치</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>감가상각누계액(기계장치)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>차량운반구</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>감가상각누계액(차량운반구)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>공구와기구</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>감가상각누계액(공구와기구)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>공구와기구</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>공구와기구(국)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>비품</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>감가상각누계액(비품)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>시설장치</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>감가상각누계액(시설장치)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>사용권자산</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>감가상각누계액(리스)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3522,7 +3417,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3914,6 +3809,226 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="22" customWidth="1" style="21" min="1" max="1"/>
+    <col width="26" customWidth="1" style="21" min="2" max="2"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
+    <col width="21.83203125" customWidth="1" style="21" min="4" max="4"/>
+    <col width="21.9140625" customWidth="1" style="21" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="21" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>유형자산계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>감가상각누계액계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>대체상대계정</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>취득원가_수동조정</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상각누계액_수동조정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>감가상각누계액(건물)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>감가상각누계액(기계장치)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>감가상각누계액(차량운반구)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>공구와기구</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>감가상각누계액(공구와기구)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>공구와기구</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>공구와기구(국)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>감가상각누계액(비품)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>감가상각누계액(시설장치)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>감가상각누계액(리스)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3960,16 +4075,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25.4140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="14.33203125" customWidth="1" style="21" min="2" max="2"/>
+    <col width="15.75" customWidth="1" style="21" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="21">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -3979,6 +4111,16 @@
           <t>국내상품매출액</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3986,6 +4128,16 @@
           <t>해외상품매출액</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3993,6 +4145,16 @@
           <t>국내제품매출액</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4000,53 +4162,48 @@
           <t>해외제품매출액</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>원자재매출</t>
+          <t>운송료매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A/S매출</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>운송료매출</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>서비스매출</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>미지급금</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>미지급금(카드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>미지급금(외화)</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -4061,173 +4218,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="28.9140625" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+    <col width="10" customWidth="1" style="21" min="2" max="2"/>
+    <col width="12" customWidth="1" style="21" min="3" max="3"/>
+    <col width="42" customWidth="1" style="21" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="21">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="21">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="21">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>선급금</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="21">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="21">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="21">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" s="21">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>국내상품매출액</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="16" customHeight="1" s="21">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>해외상품매출액</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1" s="21">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>국내제품매출액</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1" s="21">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>해외제품매출액</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
-    <col width="14.33203125" customWidth="1" style="21" min="2" max="2"/>
-    <col width="15.75" customWidth="1" style="21" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>국내상품매출액</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>해외상품매출액</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>국내제품매출액</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>해외제품매출액</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>운송료매출</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>서비스매출</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4427,211 +4616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="18.33203125" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
-    <col width="10" customWidth="1" style="21" min="2" max="2"/>
-    <col width="12" customWidth="1" style="21" min="3" max="3"/>
-    <col width="42" customWidth="1" style="21" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="21">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="21">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>선급금</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="21">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="21">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>외상매입금</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="21">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>미지급금</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="n"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="21">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>국내상품매출액</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" s="21">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>해외상품매출액</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="16" customHeight="1" s="21">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>국내제품매출액</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="21">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>해외제품매출액</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4859,6 +4844,157 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="40.9140625" bestFit="1" customWidth="1" style="21" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>주식회사 디지털그래피</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRAPHY SMA, INC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미수금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>선급금</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>미지급비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>선수금</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
